--- a/data_modelos/1_Configuración_del_puerto.xlsx
+++ b/data_modelos/1_Configuración_del_puerto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0B577A-478A-4CA0-9C83-36664D6A4284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8598F-F115-4932-87D5-522E9007EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$9:$D$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="38">
   <si>
     <t>Zona de fondeo y espera exterior</t>
   </si>
@@ -219,6 +219,30 @@
   </si>
   <si>
     <t>FB</t>
+  </si>
+  <si>
+    <t>Superficies</t>
+  </si>
+  <si>
+    <t>Pavimentos</t>
+  </si>
+  <si>
+    <t>Alumbrado</t>
+  </si>
+  <si>
+    <t>Accesos ferroviarios y terminales ferroportuarias</t>
+  </si>
+  <si>
+    <t>Accesos viarios</t>
+  </si>
+  <si>
+    <t>Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)</t>
+  </si>
+  <si>
+    <t>Zonas de Actividad Logística</t>
+  </si>
+  <si>
+    <t>Manipulación de mercancía</t>
   </si>
 </sst>
 </file>
@@ -318,12 +342,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -599,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -659,10 +721,13 @@
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="9"/>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
+        <f>+A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="2">
@@ -683,10 +748,13 @@
       <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
+        <f t="shared" ref="A4:A27" si="0">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="2">
@@ -707,10 +775,13 @@
       <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="9"/>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="2">
@@ -731,10 +802,13 @@
       <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="9"/>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="2">
@@ -755,10 +829,13 @@
       <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9"/>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="2">
@@ -767,18 +844,21 @@
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="9"/>
+      <c r="H7" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="2">
@@ -790,7 +870,7 @@
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -799,10 +879,13 @@
       <c r="G8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="9"/>
+      <c r="H8" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="2">
@@ -814,7 +897,7 @@
       <c r="D9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -823,10 +906,13 @@
       <c r="G9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="9"/>
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="2">
@@ -838,7 +924,7 @@
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -847,10 +933,13 @@
       <c r="G10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="9"/>
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="7">
@@ -865,12 +954,19 @@
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="9"/>
+      <c r="F11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="2">
@@ -885,13 +981,20 @@
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="9"/>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -917,7 +1020,8 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
@@ -943,7 +1047,8 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -969,7 +1074,8 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -989,11 +1095,14 @@
       <c r="G16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -1019,7 +1128,8 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -1039,11 +1149,14 @@
       <c r="G18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="H18" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -1054,7 +1167,7 @@
       <c r="D19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F19" s="1">
@@ -1063,24 +1176,219 @@
       <c r="G19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H19" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="F31:F38">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>$F$8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E7 E11:E18" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E27" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
       <formula1>"Activo físico, Operacional (servicios)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data_modelos/1_Configuración_del_puerto.xlsx
+++ b/data_modelos/1_Configuración_del_puerto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8598F-F115-4932-87D5-522E9007EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FBEB2F-571C-4DD3-8FA9-32385A9F312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$9:$D$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="39">
   <si>
     <t>Zona de fondeo y espera exterior</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Manipulación de mercancía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal del puerto </t>
   </si>
 </sst>
 </file>
@@ -291,7 +294,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -314,11 +317,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,39 +359,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -754,7 +743,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A27" si="0">+A3+1</f>
+        <f t="shared" ref="A4:A28" si="0">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="2">
@@ -1380,15 +1369,41 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F31:F38">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>$F$8</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E27" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
       <formula1>"Activo físico, Operacional (servicios)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data_modelos/1_Configuración_del_puerto.xlsx
+++ b/data_modelos/1_Configuración_del_puerto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FBEB2F-571C-4DD3-8FA9-32385A9F312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3F55F5-58AA-4ACD-ACF9-12ECE96E86DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$9:$D$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="39">
   <si>
     <t>Zona de fondeo y espera exterior</t>
   </si>
@@ -294,7 +294,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -315,17 +315,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -359,9 +348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -743,7 +730,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A28" si="0">+A3+1</f>
+        <f t="shared" ref="A4:A29" si="0">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="2">
@@ -1375,7 +1362,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>5</v>
@@ -1386,13 +1373,40 @@
       <c r="E28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="F28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1403,7 +1417,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E29" xr:uid="{0F46184E-0E40-4450-9C61-1B1892F4990F}">
       <formula1>"Activo físico, Operacional (servicios)"</formula1>
     </dataValidation>
   </dataValidations>
